--- a/mcd_valuation_output.xlsx
+++ b/mcd_valuation_output.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sommaire" sheetId="1" state="visible" r:id="rId3"/>
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Synthèse de valorisation — MCD</t>
   </si>
   <si>
-    <t xml:space="preserve">Généré le 21/09/2026</t>
+    <t xml:space="preserve">Généré le 26/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">VALORISATION</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Range analystes (low - high)</t>
   </si>
   <si>
-    <t xml:space="preserve">250.00 - 407.00</t>
+    <t xml:space="preserve">250.00 - 390.00</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre d'analystes</t>
@@ -213,7 +213,7 @@
     <t xml:space="preserve">Marge d'EBIT</t>
   </si>
   <si>
-    <t xml:space="preserve">Moyenne des 3 derniers exercices (yfinance) (Bear/Bull = delta ± 2% vs Base)</t>
+    <t xml:space="preserve">Moyenne pondérée des 3 derniers exercices (yfinance), poids croissants vers l'exercice le plus récent (Bear/Bull = delta ± 2% vs Base)</t>
   </si>
   <si>
     <t xml:space="preserve">Croissance perpétuelle (g)</t>
@@ -1779,18 +1779,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
               <a:t>Football Field</a:t>
@@ -1828,7 +1827,7 @@
           </c:tx>
           <c:spPr>
             <a:noFill/>
-            <a:ln w="0">
+            <a:ln w="12600">
               <a:noFill/>
             </a:ln>
           </c:spPr>
@@ -1839,7 +1838,8 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
@@ -1851,7 +1851,6 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1885,16 +1884,16 @@
                 <c:formatCode>\$#,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>170.589454836229</c:v>
+                  <c:v>123.163946411944</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50.5662575500935</c:v>
+                  <c:v>49.4644804602153</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>247.65</c:v>
+                  <c:v>234.03</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>246.9988</c:v>
+                  <c:v>235.3175</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1916,9 +1915,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1f3864"/>
+              <a:srgbClr val="1F3864"/>
             </a:solidFill>
-            <a:ln w="0">
+            <a:ln w="12600">
               <a:noFill/>
             </a:ln>
           </c:spPr>
@@ -1929,7 +1928,8 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
@@ -1941,7 +1941,6 @@
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1975,16 +1974,16 @@
                 <c:formatCode>\$#,##0.00</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>298.661135954482</c:v>
+                  <c:v>179.771697473426</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>183.971329168926</c:v>
+                  <c:v>174.72278971216</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94.1</c:v>
+                  <c:v>107.72</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.48240000000001</c:v>
+                  <c:v>2.36500000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1992,11 +1991,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="88069809"/>
-        <c:axId val="60319263"/>
+        <c:axId val="23825157"/>
+        <c:axId val="28088556"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="88069809"/>
+        <c:axId val="23825157"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2009,18 +2008,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Calibri"/>
                   </a:rPr>
                   <a:t>Valeur par action</a:t>
@@ -2053,16 +2051,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60319263"/>
+        <c:crossAx val="28088556"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2070,7 +2069,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60319263"/>
+        <c:axId val="28088556"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2103,21 +2102,21 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88069809"/>
+        <c:crossAx val="23825157"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:noFill/>
         <a:ln w="0">
           <a:noFill/>
         </a:ln>
@@ -2127,17 +2126,235 @@
     <c:dispBlanksAs val="gap"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2146,22 +2363,22 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>160920</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>162000</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="7025760" y="571680"/>
+        <a:off x="7095960" y="601200"/>
         <a:ext cx="7199640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -2183,34 +2400,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -2221,11 +2438,69 @@
         <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -2356,7 +2631,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
@@ -2384,7 +2659,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">'DCF - Modèle'!B62</f>
-        <v>248.24</v>
+        <v>236.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2393,7 +2668,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">'DCF - Modèle'!B61</f>
-        <v>281.352641438111</v>
+        <v>196.846574514943</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2411,7 +2686,7 @@
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">'Comps - Résultat'!D16</f>
-        <v>168.895865831059</v>
+        <v>164.558910453724</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2420,7 +2695,7 @@
       </c>
       <c r="B9" s="9" t="n">
         <f aca="false">'DCF - Modèle'!B63</f>
-        <v>1.13338962873877</v>
+        <v>0.832332238963819</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2429,7 +2704,7 @@
       </c>
       <c r="B10" s="10" t="n">
         <f aca="false">'DCF - Modèle'!B21</f>
-        <v>0.0540312239782107</v>
+        <v>0.0645865904657637</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2447,7 +2722,7 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">'DCF - Modèle'!E26</f>
-        <v>0.459657358427811</v>
+        <v>0.459697949553356</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2461,7 +2736,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="n">
-        <v>170.589454836229</v>
+        <v>123.163946411944</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2469,7 +2744,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="13" t="n">
-        <v>281.352641438111</v>
+        <v>196.846574514943</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2477,7 +2752,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="14" t="n">
-        <v>469.250590790712</v>
+        <v>302.93564388537</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2491,7 +2766,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="17" t="n">
-        <v>311.5484</v>
+        <v>300.27585</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2507,7 +2782,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2592,7 +2867,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="13"/>
@@ -2644,7 +2919,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="30" t="n">
-        <v>0.414</v>
+        <v>0.702857142857143</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>41</v>
@@ -2677,7 +2952,7 @@
         <v>46</v>
       </c>
       <c r="B9" s="31" t="n">
-        <v>175664.939008</v>
+        <v>167357.218816</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2701,7 +2976,7 @@
         <v>49</v>
       </c>
       <c r="B12" s="32" t="n">
-        <v>707.641552562037</v>
+        <v>707.641517192389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2740,7 +3015,7 @@
       </c>
       <c r="B18" s="34" t="n">
         <f aca="false">B4+B6*B5</f>
-        <v>0.0627</v>
+        <v>0.0771428571428572</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2749,7 +3024,7 @@
       </c>
       <c r="B19" s="34" t="n">
         <f aca="false">B9/(B9+B10)</f>
-        <v>0.7621734973446</v>
+        <v>0.753280374064129</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2758,7 +3033,7 @@
       </c>
       <c r="B20" s="34" t="n">
         <f aca="false">1-B19</f>
-        <v>0.237826502655401</v>
+        <v>0.246719625935871</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2767,7 +3042,7 @@
       </c>
       <c r="B21" s="36" t="n">
         <f aca="false">B19*B18+B20*B7*(1-B8)</f>
-        <v>0.0540312239782107</v>
+        <v>0.0645865904657637</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2811,17 +3086,17 @@
         <v>60</v>
       </c>
       <c r="B26" s="44" t="n">
-        <v>0.439657358427811</v>
+        <v>0.439697949553356</v>
       </c>
       <c r="C26" s="44" t="n">
-        <v>0.459657358427811</v>
+        <v>0.459697949553356</v>
       </c>
       <c r="D26" s="44" t="n">
-        <v>0.479657358427811</v>
+        <v>0.479697949553356</v>
       </c>
       <c r="E26" s="45" t="n">
         <f aca="false">CHOOSE($B$24,B26,C26,D26)</f>
-        <v>0.459657358427811</v>
+        <v>0.459697949553356</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>61</v>
@@ -3033,23 +3308,23 @@
       </c>
       <c r="B40" s="58" t="n">
         <f aca="false">B39*$E$26</f>
-        <v>12605.0458429583</v>
+        <v>12606.1589612168</v>
       </c>
       <c r="C40" s="58" t="n">
         <f aca="false">C39*$E$26</f>
-        <v>12857.1467598175</v>
+        <v>12858.2821404412</v>
       </c>
       <c r="D40" s="58" t="n">
         <f aca="false">D39*$E$26</f>
-        <v>13050.0039612148</v>
+        <v>13051.1563725478</v>
       </c>
       <c r="E40" s="58" t="n">
         <f aca="false">E39*$E$26</f>
-        <v>13245.754020633</v>
+        <v>13246.923718136</v>
       </c>
       <c r="F40" s="59" t="n">
         <f aca="false">F39*$E$26</f>
-        <v>13378.2115608393</v>
+        <v>13379.3929553174</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3058,23 +3333,23 @@
       </c>
       <c r="B41" s="55" t="n">
         <f aca="false">B40*(1-$B$8)</f>
-        <v>9453.78438221876</v>
+        <v>9454.61922091262</v>
       </c>
       <c r="C41" s="55" t="n">
         <f aca="false">C40*(1-$B$8)</f>
-        <v>9642.86006986313</v>
+        <v>9643.71160533087</v>
       </c>
       <c r="D41" s="55" t="n">
         <f aca="false">D40*(1-$B$8)</f>
-        <v>9787.50297091108</v>
+        <v>9788.36727941084</v>
       </c>
       <c r="E41" s="55" t="n">
         <f aca="false">E40*(1-$B$8)</f>
-        <v>9934.31551547475</v>
+        <v>9935.192788602</v>
       </c>
       <c r="F41" s="56" t="n">
         <f aca="false">F40*(1-$B$8)</f>
-        <v>10033.6586706295</v>
+        <v>10034.544716488</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3158,23 +3433,23 @@
       </c>
       <c r="B45" s="60" t="n">
         <f aca="false">B41+B42-B43-B44</f>
-        <v>8768.21688221876</v>
+        <v>8769.05172091262</v>
       </c>
       <c r="C45" s="60" t="n">
         <f aca="false">C41+C42-C43-C44</f>
-        <v>8943.58121986313</v>
+        <v>8944.43275533087</v>
       </c>
       <c r="D45" s="60" t="n">
         <f aca="false">D41+D42-D43-D44</f>
-        <v>9077.73493816108</v>
+        <v>9078.59924666084</v>
       </c>
       <c r="E45" s="60" t="n">
         <f aca="false">E41+E42-E43-E44</f>
-        <v>9213.9009622335</v>
+        <v>9214.77823536075</v>
       </c>
       <c r="F45" s="61" t="n">
         <f aca="false">F41+F42-F43-F44</f>
-        <v>9306.03997185583</v>
+        <v>9306.92601771436</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3203,23 +3478,23 @@
       </c>
       <c r="B47" s="64" t="n">
         <f aca="false">1/(1+$B$21)^B46</f>
-        <v>0.948738497732276</v>
+        <v>0.939331764044194</v>
       </c>
       <c r="C47" s="64" t="n">
         <f aca="false">1/(1+$B$21)^C46</f>
-        <v>0.900104737079297</v>
+        <v>0.882344162942378</v>
       </c>
       <c r="D47" s="64" t="n">
         <f aca="false">1/(1+$B$21)^D46</f>
-        <v>0.853964016058317</v>
+        <v>0.828813899070762</v>
       </c>
       <c r="E47" s="64" t="n">
         <f aca="false">1/(1+$B$21)^E46</f>
-        <v>0.81018853771259</v>
+        <v>0.778531221878486</v>
       </c>
       <c r="F47" s="65" t="n">
         <f aca="false">1/(1+$B$21)^F46</f>
-        <v>0.768657056149352</v>
+        <v>0.7312991060106</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3228,23 +3503,23 @@
       </c>
       <c r="B48" s="67" t="n">
         <f aca="false">B45*B47</f>
-        <v>8318.74491262701</v>
+        <v>8237.04882199963</v>
       </c>
       <c r="C48" s="67" t="n">
         <f aca="false">C45*C47</f>
-        <v>8050.15982245224</v>
+        <v>7892.06803249681</v>
       </c>
       <c r="D48" s="67" t="n">
         <f aca="false">D45*D47</f>
-        <v>7752.05898450494</v>
+        <v>7524.46923972585</v>
       </c>
       <c r="E48" s="67" t="n">
         <f aca="false">E45*E47</f>
-        <v>7464.99694722058</v>
+        <v>7173.99255891468</v>
       </c>
       <c r="F48" s="68" t="n">
         <f aca="false">F45*F47</f>
-        <v>7153.1532891749</v>
+        <v>6806.1466764613</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3259,7 +3534,7 @@
       </c>
       <c r="B51" s="56" t="n">
         <f aca="false">F45*(1+E27)/(B21-E27)</f>
-        <v>278925.047696508</v>
+        <v>212912.995564395</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3268,7 +3543,7 @@
       </c>
       <c r="B52" s="69" t="n">
         <f aca="false">B51*F47</f>
-        <v>214397.706048715</v>
+        <v>155703.083314281</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3283,7 +3558,7 @@
       </c>
       <c r="B55" s="70" t="n">
         <f aca="false">SUM(B48:F48)</f>
-        <v>38739.1139559797</v>
+        <v>37633.7253295983</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3292,7 +3567,7 @@
       </c>
       <c r="B56" s="70" t="n">
         <f aca="false">B52</f>
-        <v>214397.706048715</v>
+        <v>155703.083314281</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3301,7 +3576,7 @@
       </c>
       <c r="B57" s="61" t="n">
         <f aca="false">B55+B56</f>
-        <v>253136.820004695</v>
+        <v>193336.808643879</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3319,7 +3594,7 @@
       </c>
       <c r="B59" s="61" t="n">
         <f aca="false">B57-B58</f>
-        <v>199096.820004695</v>
+        <v>139296.808643879</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3328,7 +3603,7 @@
       </c>
       <c r="B60" s="71" t="n">
         <f aca="false">B12</f>
-        <v>707.641552562037</v>
+        <v>707.641517192389</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3337,7 +3612,7 @@
       </c>
       <c r="B61" s="72" t="n">
         <f aca="false">B59/B60</f>
-        <v>281.352641438111</v>
+        <v>196.846574514943</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3345,7 +3620,7 @@
         <v>3</v>
       </c>
       <c r="B62" s="73" t="n">
-        <v>248.24</v>
+        <v>236.5</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3354,7 +3629,7 @@
       </c>
       <c r="B63" s="74" t="n">
         <f aca="false">B61/B62</f>
-        <v>1.13338962873877</v>
+        <v>0.832332238963819</v>
       </c>
     </row>
   </sheetData>
@@ -3383,7 +3658,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="12"/>
   </cols>
@@ -3420,127 +3695,127 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="77" t="n">
-        <v>0.034</v>
+        <v>0.0446</v>
       </c>
       <c r="B4" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A4)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+B$3))/($A4-B$3)/(1+$A4)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>449.788582858793</v>
+        <v>288.51119371252</v>
       </c>
       <c r="C4" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A4)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+C$3))/($A4-C$3)/(1+$A4)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>575.934905178854</v>
+        <v>342.436803548644</v>
       </c>
       <c r="D4" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A4)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+D$3))/($A4-D$3)/(1+$A4)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>792.185743441816</v>
+        <v>418.283392992949</v>
       </c>
       <c r="E4" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A4)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+E$3))/($A4-E$3)/(1+$A4)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>1248.71529088585</v>
+        <v>532.827221949655</v>
       </c>
       <c r="F4" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A4)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+F$3))/($A4-F$3)/(1+$A4)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>2846.56870693995</v>
+        <v>725.825728273966</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="77" t="n">
-        <v>0.044</v>
+        <v>0.0546</v>
       </c>
       <c r="B5" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A5)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+B$3))/($A5-B$3)/(1+$A5)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>294.921662591506</v>
+        <v>206.614798487922</v>
       </c>
       <c r="C5" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A5)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+C$3))/($A5-C$3)/(1+$A5)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>351.057820047438</v>
+        <v>236.71586257651</v>
       </c>
       <c r="D5" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A5)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+D$3))/($A5-D$3)/(1+$A5)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>430.584043110008</v>
+        <v>275.51665617047</v>
       </c>
       <c r="E5" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A5)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+E$3))/($A5-E$3)/(1+$A5)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>551.966173047615</v>
+        <v>327.425825978605</v>
       </c>
       <c r="F5" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A5)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+F$3))/($A5-F$3)/(1+$A5)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>760.049824369226</v>
+        <v>400.436284326633</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="77" t="n">
-        <v>0.054</v>
+        <v>0.0646</v>
       </c>
       <c r="B6" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A6)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+B$3))/($A6-B$3)/(1+$A6)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>210.451428272141</v>
+        <v>154.719112404721</v>
       </c>
       <c r="C6" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A6)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+C$3))/($A6-C$3)/(1+$A6)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>241.500016969549</v>
+        <v>173.622637339205</v>
       </c>
       <c r="D6" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A6)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+D$3))/($A6-D$3)/(1+$A6)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>281.680543519137</v>
+        <v>196.764620779179</v>
       </c>
       <c r="E6" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A6)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+E$3))/($A6-E$3)/(1+$A6)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>335.716424051341</v>
+        <v>225.750539431267</v>
       </c>
       <c r="F6" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A6)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+F$3))/($A6-F$3)/(1+$A6)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>412.267254805296</v>
+        <v>263.113891219797</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="77" t="n">
-        <v>0.064</v>
+        <v>0.0746</v>
       </c>
       <c r="B7" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A7)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+B$3))/($A7-B$3)/(1+$A7)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>157.268522927346</v>
+        <v>118.891848762853</v>
       </c>
       <c r="C7" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A7)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+C$3))/($A7-C$3)/(1+$A7)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>176.657961743967</v>
+        <v>131.700306462978</v>
       </c>
       <c r="D7" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A7)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+D$3))/($A7-D$3)/(1+$A7)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>200.454091200729</v>
+        <v>146.854635536752</v>
       </c>
       <c r="E7" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A7)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+E$3))/($A7-E$3)/(1+$A7)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>230.351792313071</v>
+        <v>165.064272891529</v>
       </c>
       <c r="F7" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A7)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+F$3))/($A7-F$3)/(1+$A7)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>269.042934929043</v>
+        <v>187.356788576973</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="77" t="n">
-        <v>0.074</v>
+        <v>0.0846</v>
       </c>
       <c r="B8" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A8)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+B$3))/($A8-B$3)/(1+$A8)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>120.706941413088</v>
+        <v>92.6711188649709</v>
       </c>
       <c r="C8" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A8)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+C$3))/($A8-C$3)/(1+$A8)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>133.794917119416</v>
+        <v>101.823550499639</v>
       </c>
       <c r="D8" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A8)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+D$3))/($A8-D$3)/(1+$A8)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>149.306592030619</v>
+        <v>112.392767217074</v>
       </c>
       <c r="E8" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A8)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+E$3))/($A8-E$3)/(1+$A8)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>167.983914882885</v>
+        <v>124.735342444145</v>
       </c>
       <c r="F8" s="78" t="n">
         <f aca="false">IFERROR((SUMPRODUCT('DCF - Modèle'!$B$45:$F$45,1/(1+$A8)^'DCF - Modèle'!$B$46:$F$46)+('DCF - Modèle'!$F$45*(1+F$3))/($A8-F$3)/(1+$A8)^'DCF - Modèle'!$F$46-'DCF - Modèle'!$B$11)/'DCF - Modèle'!$B$12,"n/a")</f>
-        <v>190.906083837937</v>
+        <v>139.338462584599</v>
       </c>
     </row>
   </sheetData>
@@ -3572,7 +3847,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="33"/>
@@ -3621,22 +3896,22 @@
         <v>105</v>
       </c>
       <c r="C4" s="81" t="n">
-        <v>37657.624576</v>
+        <v>37832.278016</v>
       </c>
       <c r="D4" s="81" t="n">
-        <v>50388.619264</v>
+        <v>50563.2768</v>
       </c>
       <c r="E4" s="82" t="n">
-        <v>17.40101</v>
+        <v>17.86469</v>
       </c>
       <c r="F4" s="82" t="n">
-        <v>19.723001</v>
+        <v>20.00511</v>
       </c>
       <c r="G4" s="82" t="n">
-        <v>16.424</v>
+        <v>16.481</v>
       </c>
       <c r="H4" s="82" t="n">
-        <v>5.777</v>
+        <v>5.797</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3647,22 +3922,22 @@
         <v>107</v>
       </c>
       <c r="C5" s="81" t="n">
-        <v>33387.126784</v>
+        <v>32819.070976</v>
       </c>
       <c r="D5" s="81" t="n">
-        <v>41511.489536</v>
+        <v>41079.02976</v>
       </c>
       <c r="E5" s="82" t="n">
-        <v>18.311558</v>
+        <v>18.182741</v>
       </c>
       <c r="F5" s="82" t="n">
-        <v>16.446196</v>
+        <v>16.166376</v>
       </c>
       <c r="G5" s="82" t="n">
-        <v>14.197</v>
+        <v>14.049</v>
       </c>
       <c r="H5" s="82" t="n">
-        <v>4.28</v>
+        <v>4.235</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3673,22 +3948,22 @@
         <v>109</v>
       </c>
       <c r="C6" s="81" t="n">
-        <v>109246.201856</v>
+        <v>108140.404736</v>
       </c>
       <c r="D6" s="81" t="n">
-        <v>128096.198656</v>
+        <v>126990.401536</v>
       </c>
       <c r="E6" s="82" t="n">
-        <v>55.393063</v>
+        <v>54.83237</v>
       </c>
       <c r="F6" s="82" t="n">
-        <v>30.687695</v>
+        <v>30.377071</v>
       </c>
       <c r="G6" s="82" t="n">
-        <v>22.703</v>
+        <v>22.507</v>
       </c>
       <c r="H6" s="82" t="n">
-        <v>3.341</v>
+        <v>3.312</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3699,22 +3974,22 @@
         <v>111</v>
       </c>
       <c r="C7" s="81" t="n">
-        <v>1285.115264</v>
+        <v>1248.888064</v>
       </c>
       <c r="D7" s="81" t="n">
-        <v>5016.429568</v>
+        <v>4980.201984</v>
       </c>
       <c r="E7" s="82" t="n">
-        <v>10.21212</v>
+        <v>9.924242</v>
       </c>
       <c r="F7" s="82" t="n">
-        <v>12.911877</v>
+        <v>12.636494</v>
       </c>
       <c r="G7" s="82" t="n">
-        <v>11.002</v>
+        <v>10.923</v>
       </c>
       <c r="H7" s="82" t="n">
-        <v>2.276</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3725,22 +4000,22 @@
         <v>113</v>
       </c>
       <c r="C8" s="81" t="n">
-        <v>9732.646912</v>
+        <v>9664.498688</v>
       </c>
       <c r="D8" s="81" t="n">
-        <v>14690.663424</v>
+        <v>14622.5152</v>
       </c>
       <c r="E8" s="82" t="n">
-        <v>16.668556</v>
+        <v>16.551842</v>
       </c>
       <c r="F8" s="82" t="n">
-        <v>14.104143</v>
+        <v>14.004943</v>
       </c>
       <c r="G8" s="82" t="n">
-        <v>14.353</v>
+        <v>14.287</v>
       </c>
       <c r="H8" s="82" t="n">
-        <v>2.922</v>
+        <v>2.908</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3751,22 +4026,22 @@
         <v>115</v>
       </c>
       <c r="C9" s="81" t="n">
-        <v>42302.922752</v>
+        <v>39645.544448</v>
       </c>
       <c r="D9" s="81" t="n">
-        <v>47044.263936</v>
+        <v>44386.885632</v>
       </c>
       <c r="E9" s="82" t="n">
-        <v>30.953703</v>
+        <v>29.009258</v>
       </c>
       <c r="F9" s="82" t="n">
-        <v>24.398611</v>
+        <v>22.846933</v>
       </c>
       <c r="G9" s="82" t="n">
-        <v>20.679</v>
+        <v>19.511</v>
       </c>
       <c r="H9" s="82" t="n">
-        <v>3.787</v>
+        <v>3.573</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3777,22 +4052,22 @@
         <v>117</v>
       </c>
       <c r="C10" s="81" t="n">
-        <v>23762.020352</v>
+        <v>22679.965696</v>
       </c>
       <c r="D10" s="81" t="n">
-        <v>31701.23776</v>
+        <v>31042.400256</v>
       </c>
       <c r="E10" s="82" t="n">
-        <v>20.045979</v>
+        <v>19.133142</v>
       </c>
       <c r="F10" s="82" t="n">
-        <v>16.881163</v>
+        <v>16.112444</v>
       </c>
       <c r="G10" s="82" t="n">
-        <v>14.989</v>
+        <v>14.49</v>
       </c>
       <c r="H10" s="82" t="n">
-        <v>2.4</v>
+        <v>2.322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3817,7 +4092,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
@@ -3873,7 +4148,7 @@
       </c>
       <c r="B9" s="86" t="n">
         <f aca="false">'DCF - Modèle'!$B$12</f>
-        <v>707.641552562037</v>
+        <v>707.641517192389</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3896,15 +4171,15 @@
       </c>
       <c r="B13" s="82" t="n">
         <f aca="false">MEDIAN('Comps - Peers'!G:G)</f>
-        <v>14.989</v>
+        <v>14.49</v>
       </c>
       <c r="C13" s="81" t="n">
         <f aca="false">B13*$B$5</f>
-        <v>220008.542</v>
+        <v>212684.22</v>
       </c>
       <c r="D13" s="78" t="n">
         <f aca="false">(C13-$B$8)/$B$9</f>
-        <v>234.537586719019</v>
+        <v>224.187270172376</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3913,15 +4188,15 @@
       </c>
       <c r="B14" s="82" t="n">
         <f aca="false">MEDIAN('Comps - Peers'!H:H)</f>
-        <v>3.341</v>
+        <v>3.312</v>
       </c>
       <c r="C14" s="81" t="n">
         <f aca="false">B14*$B$4</f>
-        <v>89822.785</v>
+        <v>89043.12</v>
       </c>
       <c r="D14" s="78" t="n">
         <f aca="false">(C14-$B$8)/$B$9</f>
-        <v>50.5662575500935</v>
+        <v>49.4644804602153</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3930,15 +4205,15 @@
       </c>
       <c r="B15" s="82" t="n">
         <f aca="false">MEDIAN('Comps - Peers'!E:E)</f>
-        <v>18.311558</v>
+        <v>18.182741</v>
       </c>
       <c r="C15" s="81" t="n">
         <f aca="false">B15*$B$6</f>
-        <v>156801.871154</v>
+        <v>155698.811183</v>
       </c>
       <c r="D15" s="78" t="n">
         <f aca="false">C15/$B$9</f>
-        <v>221.583753224064</v>
+        <v>220.024980728582</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3947,7 +4222,7 @@
       </c>
       <c r="D16" s="87" t="n">
         <f aca="false">AVERAGE(D13:D15)</f>
-        <v>168.895865831059</v>
+        <v>164.558910453724</v>
       </c>
     </row>
   </sheetData>
@@ -3967,12 +4242,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4004,14 +4279,14 @@
         <v>134</v>
       </c>
       <c r="B5" s="78" t="n">
-        <v>170.589454836229</v>
+        <v>123.163946411944</v>
       </c>
       <c r="C5" s="78" t="n">
         <f aca="false">D5-B5</f>
-        <v>298.661135954482</v>
+        <v>179.771697473426</v>
       </c>
       <c r="D5" s="78" t="n">
-        <v>469.250590790712</v>
+        <v>302.93564388537</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4019,14 +4294,14 @@
         <v>135</v>
       </c>
       <c r="B6" s="78" t="n">
-        <v>50.5662575500935</v>
+        <v>49.4644804602153</v>
       </c>
       <c r="C6" s="78" t="n">
         <f aca="false">D6-B6</f>
-        <v>183.971329168926</v>
+        <v>174.72278971216</v>
       </c>
       <c r="D6" s="78" t="n">
-        <v>234.537586719019</v>
+        <v>224.187270172376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4034,11 +4309,11 @@
         <v>136</v>
       </c>
       <c r="B7" s="78" t="n">
-        <v>247.65</v>
+        <v>234.03</v>
       </c>
       <c r="C7" s="78" t="n">
         <f aca="false">D7-B7</f>
-        <v>94.1</v>
+        <v>107.72</v>
       </c>
       <c r="D7" s="78" t="n">
         <v>341.75</v>
@@ -4049,14 +4324,14 @@
         <v>3</v>
       </c>
       <c r="B8" s="78" t="n">
-        <v>246.9988</v>
+        <v>235.3175</v>
       </c>
       <c r="C8" s="78" t="n">
         <f aca="false">D8-B8</f>
-        <v>2.48240000000001</v>
+        <v>2.36500000000001</v>
       </c>
       <c r="D8" s="78" t="n">
-        <v>249.4812</v>
+        <v>237.6825</v>
       </c>
     </row>
   </sheetData>
@@ -4077,7 +4352,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E55"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -4972,7 +5247,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F73"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="10"/>
@@ -6223,7 +6498,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="10"/>
